--- a/AAII_Financials/Yearly/HWKN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HWKN_YR_FIN.xlsx
@@ -3028,10 +3028,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>20700</v>
+        <v>13000</v>
       </c>
       <c r="E59" s="3">
-        <v>12400</v>
+        <v>4700</v>
       </c>
       <c r="F59" s="3">
         <v>9800</v>
